--- a/Supplementary files/Metadata.xlsx
+++ b/Supplementary files/Metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/s449735/Documents/GitHub/Chytrid_meta_analysis/Supplementary files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/s449735/Documents/GitHub/Bd-Meta-analysis/Supplementary files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D998ABF-2BF5-EB44-B68B-F1B136D908CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57035FB8-F1EF-754B-95D6-477B806C0EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{206BD728-406A-4804-BCFF-F6BE7796A83A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="13720" activeTab="1" xr2:uid="{206BD728-406A-4804-BCFF-F6BE7796A83A}"/>
   </bookViews>
   <sheets>
     <sheet name="key" sheetId="15" r:id="rId1"/>
@@ -10405,19 +10405,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J7 I10:J10 H63:H1048576 H24:H61 H1:H22" xr:uid="{906A17C0-69C9-CA4A-A7D9-5F417B9CE8DB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J7 I10:J10 H61:H1048576 H24:H60 H1:H22" xr:uid="{906A17C0-69C9-CA4A-A7D9-5F417B9CE8DB}">
       <formula1>"split, independent, unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L63:M1048576 L13:M61 L1:L12 M2:M12" xr:uid="{F80747C2-5246-DA49-BF32-BF936F048F0E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L61:M1048576 L13:M60 L1:L12 M2:M12" xr:uid="{F80747C2-5246-DA49-BF32-BF936F048F0E}">
       <formula1>"larva, metamorph, juvenile, adult, cross-stage, not applicable, unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G63:G1048576 G2:G61" xr:uid="{A229FC7A-15E7-6D48-A252-828DF9FA65C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G61:G1048576 G2:G60" xr:uid="{A229FC7A-15E7-6D48-A252-828DF9FA65C9}">
       <formula1>"wild, captive, unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N63:N1048576 N2:N61" xr:uid="{99F79314-08DA-0C49-A6C8-201D2AF5DA66}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N61:N1048576 N2:N60" xr:uid="{99F79314-08DA-0C49-A6C8-201D2AF5DA66}">
       <formula1>"field, semi-natural, laboratory"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K63:K1048576 K2:K61" xr:uid="{06EC893A-D2BF-E04E-AD7D-0A8F090CEB82}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K61:K1048576 K2:K60" xr:uid="{06EC893A-D2BF-E04E-AD7D-0A8F090CEB82}">
       <formula1>"yes, no"</formula1>
     </dataValidation>
   </dataValidations>
